--- a/ZonasEscolares/excels/ANCASH-HUARAZ-INDEPENDENCIA.xlsx
+++ b/ZonasEscolares/excels/ANCASH-HUARAZ-INDEPENDENCIA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/ANCASH-HUARAZ-INDEPENDENCIA.xlsx
+++ b/ZonasEscolares/excels/ANCASH-HUARAZ-INDEPENDENCIA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,66 +413,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>123</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-9.51885</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.53191</v>
-      </c>
-      <c r="I2" t="n">
-        <v>433</v>
-      </c>
-      <c r="J2" t="n">
-        <v>17</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-9.51885</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.53191</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>282 SAN JUAN BAUTISTA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-9.51412</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.52615</v>
-      </c>
-      <c r="I3" t="n">
-        <v>211</v>
-      </c>
-      <c r="J3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-9.51412</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.52615</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>CISEA NICRUPAMPA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-9.520557</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.52337900000001</v>
-      </c>
-      <c r="I4" t="n">
-        <v>430</v>
-      </c>
-      <c r="J4" t="n">
-        <v>21</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-9.520557</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.523379</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>CISEA PALMIRA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-9.50686</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.53440000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>269</v>
-      </c>
-      <c r="J5" t="n">
-        <v>13</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-9.50686</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.5344</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>GRAN MARISCAL TORIBIO DE LUZURIAGA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-9.51493</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.53052</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2507</v>
-      </c>
-      <c r="J6" t="n">
-        <v>146</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-9.51493</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.53052</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2507</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>86002 JORGE BASADRE GROHMAN</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-9.520849999999999</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.52594000000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1602</v>
-      </c>
-      <c r="J7" t="n">
-        <v>82</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-9.52085</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.52594</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1602</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>86017 SABIO ANTONIO RAIMONDI</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-9.52182</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.52907999999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1447</v>
-      </c>
-      <c r="J8" t="n">
-        <v>74</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-9.52182</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.52908</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1447</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>86030 NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-9.535779</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.56177</v>
-      </c>
-      <c r="I9" t="n">
-        <v>278</v>
-      </c>
-      <c r="J9" t="n">
-        <v>32</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-9.535779</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.56177</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>86031 NUESTRA SEÑORA DE LA ASUNCION</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-9.475549000000001</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.53787699999999</v>
-      </c>
-      <c r="I10" t="n">
-        <v>291</v>
-      </c>
-      <c r="J10" t="n">
-        <v>25</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-9.475549</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.537877</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>86034 SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-9.513374000000001</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.503626</v>
-      </c>
-      <c r="I11" t="n">
-        <v>271</v>
-      </c>
-      <c r="J11" t="n">
-        <v>22</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-9.513374</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.503626</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>86040 SUIZA PERUANA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-9.49743</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.5365</v>
-      </c>
-      <c r="I12" t="n">
-        <v>494</v>
-      </c>
-      <c r="J12" t="n">
-        <v>28</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-9.49743</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.5365</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>87003-1 JESUS NAZARENO</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-9.511469999999999</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-77.52581000000001</v>
-      </c>
-      <c r="I13" t="n">
-        <v>295</v>
-      </c>
-      <c r="J13" t="n">
-        <v>18</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-9.51147</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-77.52581</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>COLEGIO PARROQUIAL NUESTRA SEÑORA DEL SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-9.515578</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.532393</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1393</v>
-      </c>
-      <c r="J14" t="n">
-        <v>66</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-9.515578</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.532393</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1393</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>ALBERT EINSTEIN</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-9.51802</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.53124</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1482</v>
-      </c>
-      <c r="J15" t="n">
-        <v>81</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-9.51802</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.53124</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1482</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>EL PINAR COLLEGE</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-9.513839000000001</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-77.510155</v>
-      </c>
-      <c r="I16" t="n">
-        <v>489</v>
-      </c>
-      <c r="J16" t="n">
-        <v>46</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-9.513839</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-77.510155</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>HONORES</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-9.522019999999999</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-77.52567999999999</v>
-      </c>
-      <c r="I17" t="n">
-        <v>353</v>
-      </c>
-      <c r="J17" t="n">
-        <v>38</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-9.52202</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-77.52568</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>SAN JOSE MARELLO</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-9.51699</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-77.53086</v>
-      </c>
-      <c r="I18" t="n">
-        <v>254</v>
-      </c>
-      <c r="J18" t="n">
-        <v>22</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-9.51699</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-77.53086</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>ALMIRANTE MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-9.52267</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-77.52410999999999</v>
-      </c>
-      <c r="I19" t="n">
-        <v>211</v>
-      </c>
-      <c r="J19" t="n">
-        <v>26</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-9.52267</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-77.52411</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>ALBERT EINSTEIN</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-9.52267</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-77.5258</v>
-      </c>
-      <c r="I20" t="n">
-        <v>312</v>
-      </c>
-      <c r="J20" t="n">
-        <v>14</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-9.52267</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-77.5258</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>NOBEL INGENIEROS</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-9.51319</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-77.52616</v>
-      </c>
-      <c r="I21" t="n">
-        <v>249</v>
-      </c>
-      <c r="J21" t="n">
-        <v>25</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-9.51319</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-77.52616</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>PERUANO AMERICANO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-9.51529</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-77.53194999999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>220</v>
-      </c>
-      <c r="J22" t="n">
-        <v>15</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-9.51529</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-77.53195</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>LOS ANDES RVS.</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-9.515713999999999</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-77.529273</v>
-      </c>
-      <c r="I23" t="n">
-        <v>282</v>
-      </c>
-      <c r="J23" t="n">
-        <v>23</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-9.515714</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-77.529273</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-9.52046</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-77.52659</v>
-      </c>
-      <c r="I24" t="n">
-        <v>356</v>
-      </c>
-      <c r="J24" t="n">
-        <v>15</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-9.52046</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-77.52659</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>PERUANO CANADIENSE</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-9.52346</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-77.51739000000001</v>
-      </c>
-      <c r="I25" t="n">
-        <v>373</v>
-      </c>
-      <c r="J25" t="n">
-        <v>26</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-9.52346</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-77.51739</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-9.52036</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-77.52666000000001</v>
-      </c>
-      <c r="I26" t="n">
-        <v>705</v>
-      </c>
-      <c r="J26" t="n">
-        <v>41</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-9.52036</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-77.52666</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>INTEGRAL</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-9.519477999999999</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-77.53218200000001</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1097</v>
-      </c>
-      <c r="J27" t="n">
-        <v>58</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-9.519478</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-77.532182</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1097</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>SANTO TOMAS DE AQUINO</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-9.5199</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-77.52851</v>
-      </c>
-      <c r="I28" t="n">
-        <v>492</v>
-      </c>
-      <c r="J28" t="n">
-        <v>23</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-9.5199</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-77.52851</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>PERUANO AMERICANO</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-9.51554</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-77.53146</v>
-      </c>
-      <c r="I29" t="n">
-        <v>36</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-9.51554</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-77.53146</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,22 +2245,218 @@
           <t>VICTOR VALENZUELA GUARDIA</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-9.516673000000001</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-77.531481</v>
-      </c>
-      <c r="I30" t="n">
-        <v>474</v>
-      </c>
-      <c r="J30" t="n">
-        <v>29</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-9.516673</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-77.531481</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>020105</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>HUARAZ</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>016242</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>86021 SIMON ANTONIO BOLIVAR PALACIOS</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-9.51968</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-77.5332</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2371</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>020105</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>HUARAZ</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>016440</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>86088 SEÑOR DE LOS MILAGROS</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-9.50581</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-77.534729</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>020105</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>HUARAZ</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>523259</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>LAS AMERICAS SCHOOL</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-9.516095</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-77.533275</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/ZonasEscolares/excels/ANCASH-HUARAZ-INDEPENDENCIA.xlsx
+++ b/ZonasEscolares/excels/ANCASH-HUARAZ-INDEPENDENCIA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16100</t>
+          <t>16138</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>282 SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-9.51885</t>
+          <t>-9.51412</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.53191</t>
+          <t>-77.52615</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>211</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>282 SAN JUAN BAUTISTA</t>
+          <t>CISEA PALMIRA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-9.51412</t>
+          <t>-9.50686</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.52615</t>
+          <t>-77.5344</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>269</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16195</t>
+          <t>700191</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CISEA NICRUPAMPA</t>
+          <t>ALBERT EINSTEIN</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-9.520557</t>
+          <t>-9.52267</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.523379</t>
+          <t>-77.5258</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>312</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>16218</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CISEA PALMIRA</t>
+          <t>GRAN MARISCAL TORIBIO DE LUZURIAGA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-9.50686</t>
+          <t>-9.51493</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.5344</t>
+          <t>-77.53052</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>146</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -749,37 +749,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16218</t>
+          <t>747891</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GRAN MARISCAL TORIBIO DE LUZURIAGA</t>
+          <t>PERUANO AMERICANO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-9.51493</t>
+          <t>-9.51529</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.53052</t>
+          <t>-77.53195</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2507</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16223</t>
+          <t>839254</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>86002 JORGE BASADRE GROHMAN</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-9.52085</t>
+          <t>-9.52046</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.52594</t>
+          <t>-77.52659</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>356</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16237</t>
+          <t>16100</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>86017 SABIO ANTONIO RAIMONDI</t>
+          <t>123</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-9.52182</t>
+          <t>-9.51885</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.52908</t>
+          <t>-77.53191</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>433</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>16652</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>86030 NIÑO JESUS DE PRAGA</t>
+          <t>87003-1 JESUS NAZARENO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-9.535779</t>
+          <t>-9.51147</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.56177</t>
+          <t>-77.52581</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>295</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16261</t>
+          <t>16195</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>86031 NUESTRA SEÑORA DE LA ASUNCION</t>
+          <t>CISEA NICRUPAMPA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-9.475549</t>
+          <t>-9.520557</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.537877</t>
+          <t>-77.523379</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>430</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16360</t>
+          <t>523315</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>86040 SUIZA PERUANA</t>
+          <t>SAN JOSE MARELLO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9.49743</t>
+          <t>-9.51699</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.5365</t>
+          <t>-77.53086</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>254</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>16652</t>
+          <t>834223</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>87003-1 JESUS NAZARENO</t>
+          <t>LOS ANDES RVS.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-9.51147</t>
+          <t>-9.515714</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.52581</t>
+          <t>-77.529273</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>282</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16751</t>
+          <t>862249</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>COLEGIO PARROQUIAL NUESTRA SEÑORA DEL SAGRADO CORAZON DE JESUS</t>
+          <t>SANTO TOMAS DE AQUINO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-9.515578</t>
+          <t>-9.5199</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.532393</t>
+          <t>-77.52851</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>492</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16765</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ALBERT EINSTEIN</t>
+          <t>86031 NUESTRA SEÑORA DE LA ASUNCION</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-9.51802</t>
+          <t>-9.475549</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.53124</t>
+          <t>-77.537877</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>291</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>16826</t>
+          <t>718247</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>EL PINAR COLLEGE</t>
+          <t>NOBEL INGENIEROS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-9.513839</t>
+          <t>-9.51319</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.510155</t>
+          <t>-77.52616</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>249</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>514943</t>
+          <t>700186</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>HONORES</t>
+          <t>ALMIRANTE MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-9.52202</t>
+          <t>-9.52267</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.52568</t>
+          <t>-77.52411</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>211</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>523315</t>
+          <t>844156</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SAN JOSE MARELLO</t>
+          <t>PERUANO CANADIENSE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-9.51699</t>
+          <t>-9.52346</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.53086</t>
+          <t>-77.51739</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>373</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>700186</t>
+          <t>16360</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ALMIRANTE MIGUEL GRAU SEMINARIO</t>
+          <t>86040 SUIZA PERUANA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-9.52267</t>
+          <t>-9.49743</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.52411</t>
+          <t>-77.5365</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>494</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>700191</t>
+          <t>912206</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ALBERT EINSTEIN</t>
+          <t>VICTOR VALENZUELA GUARDIA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-9.52267</t>
+          <t>-9.516673</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.5258</t>
+          <t>-77.531481</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>474</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,37 +1679,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>718247</t>
+          <t>863442</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NOBEL INGENIEROS</t>
+          <t>PERUANO AMERICANO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-9.51319</t>
+          <t>-9.51554</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.52616</t>
+          <t>-77.53146</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>747891</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PERUANO AMERICANO</t>
+          <t>86030 NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-9.51529</t>
+          <t>-9.535779</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.53195</t>
+          <t>-77.56177</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>278</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>834223</t>
+          <t>514943</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>LOS ANDES RVS.</t>
+          <t>HONORES</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-9.515714</t>
+          <t>-9.52202</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.529273</t>
+          <t>-77.52568</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>353</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>839254</t>
+          <t>849776</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-9.52046</t>
+          <t>-9.52036</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.52659</t>
+          <t>-77.52666</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>705</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>844156</t>
+          <t>16826</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PERUANO CANADIENSE</t>
+          <t>EL PINAR COLLEGE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-9.52346</t>
+          <t>-9.513839</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.51739</t>
+          <t>-77.510155</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>489</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>849776</t>
+          <t>852764</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SAN MARTIN DE PORRES</t>
+          <t>INTEGRAL</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-9.52036</t>
+          <t>-9.519478</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.52666</t>
+          <t>-77.532182</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>852764</t>
+          <t>16751</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>INTEGRAL</t>
+          <t>COLEGIO PARROQUIAL NUESTRA SEÑORA DEL SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-9.519478</t>
+          <t>-9.515578</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.532182</t>
+          <t>-77.532393</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>862249</t>
+          <t>16237</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SANTO TOMAS DE AQUINO</t>
+          <t>86017 SABIO ANTONIO RAIMONDI</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-9.5199</t>
+          <t>-9.52182</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.52851</t>
+          <t>-77.52908</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,37 +2175,37 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>863442</t>
+          <t>16765</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PERUANO AMERICANO</t>
+          <t>ALBERT EINSTEIN</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-9.51554</t>
+          <t>-9.51802</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.53146</t>
+          <t>-77.53124</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>81</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>912206</t>
+          <t>16223</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>VICTOR VALENZUELA GUARDIA</t>
+          <t>86002 JORGE BASADRE GROHMAN</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-9.516673</t>
+          <t>-9.52085</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.531481</t>
+          <t>-77.52594</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">

--- a/ZonasEscolares/excels/ANCASH-HUARAZ-INDEPENDENCIA.xlsx
+++ b/ZonasEscolares/excels/ANCASH-HUARAZ-INDEPENDENCIA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>912206</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>282 SAN JUAN BAUTISTA</t>
+          <t>VICTOR VALENZUELA GUARDIA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-9.51412</t>
+          <t>474</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.52615</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>-9.516673</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.531481</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>863442</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CISEA PALMIRA</t>
+          <t>PERUANO AMERICANO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-9.50686</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.5344</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>-9.51554</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.53146</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>700191</t>
+          <t>862249</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ALBERT EINSTEIN</t>
+          <t>SANTO TOMAS DE AQUINO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-9.52267</t>
+          <t>492</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.5258</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>-9.5199</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.52851</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16218</t>
+          <t>852764</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GRAN MARISCAL TORIBIO DE LUZURIAGA</t>
+          <t>INTEGRAL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-9.51493</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.53052</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2507</t>
+          <t>-9.519478</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>-77.532182</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>747891</t>
+          <t>849776</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PERUANO AMERICANO</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-9.51529</t>
+          <t>705</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.53195</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>-9.52036</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.52666</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>839254</t>
+          <t>844156</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SAN MARTIN DE PORRES</t>
+          <t>PERUANO CANADIENSE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-9.52046</t>
+          <t>373</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.52659</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>-9.52346</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.51739</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16100</t>
+          <t>839254</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-9.51885</t>
+          <t>356</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.53191</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>-9.52046</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.52659</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16652</t>
+          <t>834223</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>87003-1 JESUS NAZARENO</t>
+          <t>LOS ANDES RVS.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-9.51147</t>
+          <t>282</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.52581</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>-9.515714</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.529273</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16195</t>
+          <t>747891</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CISEA NICRUPAMPA</t>
+          <t>PERUANO AMERICANO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-9.520557</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.523379</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>-9.51529</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.53195</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16280</t>
+          <t>718247</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>86034 SAN MARTIN DE PORRES</t>
+          <t>NOBEL INGENIEROS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-9.513374</t>
+          <t>249</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.503626</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>-9.51319</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.52616</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>523315</t>
+          <t>700191</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SAN JOSE MARELLO</t>
+          <t>ALBERT EINSTEIN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9.51699</t>
+          <t>312</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.53086</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>-9.52267</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.5258</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>834223</t>
+          <t>700186</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LOS ANDES RVS.</t>
+          <t>ALMIRANTE MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-9.515714</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.529273</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>-9.52267</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.52411</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>862249</t>
+          <t>523315</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SANTO TOMAS DE AQUINO</t>
+          <t>SAN JOSE MARELLO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-9.5199</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.52851</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>-9.51699</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.53086</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16261</t>
+          <t>523259</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>86031 NUESTRA SEÑORA DE LA ASUNCION</t>
+          <t>LAS AMERICAS SCHOOL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-9.475549</t>
+          <t>332</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.537877</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>-9.516095</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-77.533275</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>718247</t>
+          <t>514943</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NOBEL INGENIEROS</t>
+          <t>HONORES</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-9.51319</t>
+          <t>353</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.52616</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>-9.52202</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-77.52568</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>700186</t>
+          <t>016826</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ALMIRANTE MIGUEL GRAU SEMINARIO</t>
+          <t>EL PINAR COLLEGE</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-9.52267</t>
+          <t>489</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.52411</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>-9.513839</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.510155</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>844156</t>
+          <t>016765</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PERUANO CANADIENSE</t>
+          <t>ALBERT EINSTEIN</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-9.52346</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.51739</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>-9.51802</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.53124</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16360</t>
+          <t>016751</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>86040 SUIZA PERUANA</t>
+          <t>COLEGIO PARROQUIAL NUESTRA SEÑORA DEL SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-9.49743</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.5365</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>-9.515578</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-77.532393</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>912206</t>
+          <t>016652</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VICTOR VALENZUELA GUARDIA</t>
+          <t>87003-1 JESUS NAZARENO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-9.516673</t>
+          <t>295</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.531481</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>-9.51147</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-77.52581</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,37 +1679,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>863442</t>
+          <t>016440</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PERUANO AMERICANO</t>
+          <t>86088 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-9.51554</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.53146</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-9.50581</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-77.534729</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>016360</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>86030 NIÑO JESUS DE PRAGA</t>
+          <t>86040 SUIZA PERUANA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-9.535779</t>
+          <t>494</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.56177</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>-9.49743</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-77.5365</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>514943</t>
+          <t>016280</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>HONORES</t>
+          <t>86034 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-9.52202</t>
+          <t>271</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.52568</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>-9.513374</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-77.503626</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>849776</t>
+          <t>016261</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SAN MARTIN DE PORRES</t>
+          <t>86031 NUESTRA SEÑORA DE LA ASUNCION</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-9.52036</t>
+          <t>291</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.52666</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>-9.475549</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-77.537877</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>16826</t>
+          <t>016256</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>EL PINAR COLLEGE</t>
+          <t>86030 NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-9.513839</t>
+          <t>278</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.510155</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>-9.535779</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-77.56177</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>852764</t>
+          <t>016242</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>INTEGRAL</t>
+          <t>86021 SIMON ANTONIO BOLIVAR PALACIOS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-9.519478</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.532182</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>-9.51968</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-77.5332</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>16751</t>
+          <t>016237</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>COLEGIO PARROQUIAL NUESTRA SEÑORA DEL SAGRADO CORAZON DE JESUS</t>
+          <t>86017 SABIO ANTONIO RAIMONDI</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-9.515578</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.532393</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>-9.52182</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>-77.52908</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>16237</t>
+          <t>016223</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>86017 SABIO ANTONIO RAIMONDI</t>
+          <t>86002 JORGE BASADRE GROHMAN</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-9.52182</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.52908</t>
+          <t>82</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>-9.52085</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>-77.52594</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,37 +2175,37 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16765</t>
+          <t>016218</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ALBERT EINSTEIN</t>
+          <t>GRAN MARISCAL TORIBIO DE LUZURIAGA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-9.51802</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.53124</t>
+          <t>146</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>-9.51493</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>-77.53052</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>16223</t>
+          <t>016204</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>86002 JORGE BASADRE GROHMAN</t>
+          <t>CISEA PALMIRA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-9.52085</t>
+          <t>269</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.52594</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>-9.50686</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>-77.5344</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>016242</t>
+          <t>016195</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>86021 SIMON ANTONIO BOLIVAR PALACIOS</t>
+          <t>CISEA NICRUPAMPA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-9.51968</t>
+          <t>430</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.5332</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>-9.520557</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>-77.523379</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>016440</t>
+          <t>016138</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>86088 SEÑOR DE LOS MILAGROS</t>
+          <t>282 SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-9.50581</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.534729</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>-9.51412</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-77.52615</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>523259</t>
+          <t>016100</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>LAS AMERICAS SCHOOL</t>
+          <t>123</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-9.516095</t>
+          <t>433</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.533275</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>-9.51885</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.53191</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">

--- a/ZonasEscolares/excels/ANCASH-HUARAZ-INDEPENDENCIA.xlsx
+++ b/ZonasEscolares/excels/ANCASH-HUARAZ-INDEPENDENCIA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
